--- a/Results/attachment_2_log(RV)_summary_statistics.xlsx
+++ b/Results/attachment_2_log(RV)_summary_statistics.xlsx
@@ -703,7 +703,7 @@
         <v>0.7507004229627613</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7234238991329867</v>
+        <v>0.7234238991329868</v>
       </c>
     </row>
     <row r="10">

--- a/Results/attachment_2_log(RV)_summary_statistics.xlsx
+++ b/Results/attachment_2_log(RV)_summary_statistics.xlsx
@@ -703,7 +703,7 @@
         <v>0.7507004229627613</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7234238991329868</v>
+        <v>0.7234238991329867</v>
       </c>
     </row>
     <row r="10">
